--- a/MODELO_IMPORTAR_UNIVERSO.xlsx
+++ b/MODELO_IMPORTAR_UNIVERSO.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'UNIVERSO'!$A$1:$C$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'UNIVERSO'!$A$1:$D$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,12 +31,12 @@
     <font>
       <name val="Century Gothic"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Century Gothic"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -63,7 +63,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00142C49"/>
+        <color rgb="00FFFFFF"/>
       </bottom>
     </border>
     <border>
@@ -84,9 +84,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -454,15 +454,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>N° DE ÍTEM</t>
@@ -478,259 +479,974 @@
           <t>NOMBRE COMPLETO DEL PROPONENTE</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="19" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ I</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ II</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="19" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ III</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ IV</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ V</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ VI</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ VII</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ VIII</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ IX</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ X</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ XI</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ XII</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ XII</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ XIV</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR 1-   SUPERVISOR DE CAMPO LA PAZ XV</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XVI</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XVII</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XVIII</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XIX</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XX</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXI</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXII</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXIII</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXIV</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXV</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXVI</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXVII</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXVIII</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXIX</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXX</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXXI</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXXII</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXXIII</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXXIV</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXXV</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXXVI</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXXVII</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXXVIII</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XXXIX</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XL</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XLI</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XLII</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XLIII</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XLIV</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XLV</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XLVI</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XLVII</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XLVIII</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ XLIX</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ L</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LI</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LII</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LIII</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LIV</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LV</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LVI</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LVII</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LVIII</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LIX</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIAR I -   ENCUESTADOR LA PAZ LX</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>ENCUESTADOR</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C51"/>
+  <autoFilter ref="A1:D61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -744,8 +1460,8 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="105" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -760,7 +1476,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>N° DE ÍTEM</t>
@@ -768,11 +1484,11 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Número entero o identificador numérico del ítem. No dejar vacío.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
+          <t>Número del ítem oficial (1 a 60).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CARGO / DISTRIBUCIÓN</t>
@@ -780,11 +1496,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Nombre del cargo o distribución. Usa el mismo texto en todas las filas del mismo ítem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>El modelo incluye los 60 cargos oficiales como guía. Si un ítem tiene varias personas, repite el mismo número y cargo en otra fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NOMBRE COMPLETO DEL PROPONENTE</t>
@@ -792,35 +1508,35 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Una persona por fila. No combinar celdas ni colocar títulos antes de los encabezados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
+          <t>Escribe una persona por fila. Esta columna debe estar completa para importar esa fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Referencia informativa: SUPERVISOR o ENCUESTADOR. El sistema calcula el criterio de experiencia según el cargo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>IMPORTAR</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>En la aplicación, selecciona “Importar otro universo” y elige este archivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SEPARACIÓN</t>
-        </is>
-      </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>El sistema crea una pestaña independiente por universo. Los registros de cada universo se guardan en Cloudflare D1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+          <t>En la aplicación selecciona “Importar otro universo” y elige este archivo. El importador detecta los encabezados y omite títulos o filas anteriores al encabezado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>IMPORTANTE</t>
@@ -828,7 +1544,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>No cambies los encabezados de la hoja UNIVERSO. Puedes agregar todas las filas necesarias debajo de la primera fila.</t>
+          <t>No combines celdas en la hoja UNIVERSO. Puedes insertar o duplicar filas para incluir todas las personas del universo.</t>
         </is>
       </c>
     </row>

--- a/MODELO_IMPORTAR_UNIVERSO.xlsx
+++ b/MODELO_IMPORTAR_UNIVERSO.xlsx
@@ -727,7 +727,7 @@
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="2" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="2" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="2" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="2" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="2" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="2" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="2" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="2" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="2" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="2" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="2" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="2" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="2" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="2" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="2" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="2" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="2" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="2" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="2" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="2" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="2" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="2" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="2" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="2" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="2" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="2" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="2" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="2" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="2" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="2" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="2" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="2" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Número del ítem oficial (1 a 60).</t>
+          <t>Numeración visible por tipo: supervisor 1–15 y encuestador 1–45.</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>El modelo incluye los 60 cargos oficiales como guía. Si un ítem tiene varias personas, repite el mismo número y cargo en otra fila.</t>
+          <t>El modelo incluye los cargos con numeración independiente por tipo oficiales como guía. Si un ítem tiene varias personas, repite el mismo número y cargo en otra fila.</t>
         </is>
       </c>
     </row>
